--- a/src/test/java/utilities/Project.xlsx
+++ b/src/test/java/utilities/Project.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2445031_cognizant_com/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC10481F795F67DC5ADE58FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDE585F8-386E-4CD7-99C0-F72174500811}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{D9813E10-B878-4C24-ADEA-8C97AEF8FA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:O9"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>New Delhi</t>
   </si>
@@ -37,13 +33,19 @@
   </si>
   <si>
     <t>21</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Team%pjt@cognizant.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,6 +58,14 @@
       <color rgb="FF2A00FF"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -75,16 +85,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -98,10 +111,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -369,6 +378,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -382,13 +394,27 @@
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>7856789765</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D6" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{212140D0-63A6-46FE-90EF-9B9FAE39ABD5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>